--- a/ttl_long/AdHoc_Net_10.xlsx
+++ b/ttl_long/AdHoc_Net_10.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>136</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>85</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>191</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>355</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>266</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>241</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>171</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>316</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>203</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>336</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>337</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>379</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>527</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>259</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>520</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>346</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>482</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>583</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>504</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>599</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>632</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>742</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>306</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>683</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>838</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>262</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>863</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>311</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>834</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>958</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>883</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>966</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1048</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>117</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1063</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>293</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1041</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1095</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1081</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,199 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1178</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1253</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1244</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1646</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1626</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,7 +1227,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1062,7 +1249,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1084,7 +1271,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1106,7 +1293,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1128,7 +1315,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1150,7 +1337,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1189,7 +1376,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1216,7 +1403,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1238,7 +1425,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1255,12 +1442,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1282,7 +1469,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1304,7 +1491,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1321,12 +1508,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1348,7 +1535,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1370,7 +1557,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1436,7 +1623,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1458,7 +1645,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1502,7 +1689,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1524,7 +1711,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1546,7 +1733,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1568,7 +1755,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1590,7 +1777,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1607,12 +1794,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1634,7 +1821,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1656,7 +1843,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1678,7 +1865,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1695,12 +1882,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1722,7 +1909,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1739,12 +1926,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1761,12 +1948,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1783,12 +1970,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1805,12 +1992,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1832,7 +2019,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1854,7 +2041,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1876,7 +2063,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1898,7 +2085,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1920,7 +2107,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1942,7 +2129,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1964,7 +2151,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1986,7 +2173,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2008,7 +2195,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2025,12 +2212,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2047,12 +2234,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2074,7 +2261,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2091,12 +2278,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2113,7 +2300,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2140,7 +2327,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2157,7 +2344,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2184,7 +2371,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2206,7 +2393,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2228,7 +2415,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2250,7 +2437,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2272,7 +2459,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2289,12 +2476,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2316,7 +2503,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2338,7 +2525,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2360,7 +2547,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2382,7 +2569,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2399,12 +2586,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2421,12 +2608,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2443,12 +2630,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2465,12 +2652,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2487,12 +2674,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2509,12 +2696,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2531,12 +2718,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2553,12 +2740,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2575,12 +2762,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2597,12 +2784,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2619,12 +2806,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2641,12 +2828,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2663,12 +2850,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2685,12 +2872,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2707,7 +2894,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2729,7 +2916,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2751,12 +2938,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2773,12 +2960,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2795,12 +2982,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2817,12 +3004,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2839,12 +3026,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2861,12 +3048,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2883,20 +3070,922 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2945,7 +4034,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -2971,7 +4060,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_10.xlsx
+++ b/ttl_long/AdHoc_Net_10.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>408</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>969</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>108</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>336</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>269</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>271</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>248</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>245</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>306</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>174</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>314</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>287</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>400</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>546</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>271</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>441</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>509</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>534</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>627</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>316</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>621</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>774</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>832</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>714</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>789</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>184</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>836</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>886</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>974</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>271</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>993</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>984</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1038</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1137</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1157</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1238</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1296</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>282</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1278</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1370</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1301</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1326</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1562</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1408</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>310</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1505</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1591</t>
         </is>
       </c>
     </row>
@@ -1123,63 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1463</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1529</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1646</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1626</t>
+          <t>1697</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1227,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1249,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1271,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1293,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1315,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1359,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1381,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1403,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1425,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1469,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1491,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1513,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1557,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1574,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1623,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1645,7 +1594,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1667,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1689,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1706,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1750,7 +1699,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1777,7 +1726,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1794,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1816,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1843,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1865,7 +1814,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1882,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1909,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1926,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1948,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1970,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1992,7 +1941,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2014,7 +1963,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2036,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2058,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2080,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2102,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2124,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2146,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2168,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2190,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2212,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2234,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2256,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2278,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2300,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2322,7 +2271,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2344,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2366,7 +2315,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2388,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2410,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2432,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2454,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2476,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2498,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2520,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2542,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2564,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2586,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2608,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2630,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2652,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2674,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2696,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2718,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2740,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2762,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2784,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2806,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2828,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2850,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2872,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2894,7 +2843,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2916,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2938,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2960,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2982,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3009,7 +2958,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3026,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3048,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3075,7 +3024,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3092,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3141,7 +3090,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3158,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3207,7 +3156,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3246,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3273,7 +3222,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3290,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3312,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3334,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3356,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3378,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3400,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3422,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3444,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3466,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3488,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3510,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3532,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3554,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3581,7 +3530,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3603,7 +3552,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3620,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3647,7 +3596,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3664,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3691,7 +3640,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3713,7 +3662,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3730,12 +3679,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3752,12 +3701,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3766,226 +3715,6 @@
         </is>
       </c>
       <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -4034,7 +3763,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -4054,7 +3783,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_10.xlsx
+++ b/ttl_long/AdHoc_Net_10.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>217</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>176</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>145</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>329</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>334</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>239</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>328</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>305</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>398</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>513</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>154</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>473</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>484</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>691</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>581</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>341</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>641</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>762</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>251</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>710</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>757</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>924</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>868</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>309</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>828</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>990</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>205</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1073</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1025</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1168</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1096</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1120</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1191</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1274</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>337</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1259</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1361</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>150</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1326</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1388</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1454</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>192</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1486</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>1456</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1628</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1554</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1325,7 +1325,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1369,12 +1369,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1677,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1809,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1853,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1875,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1985,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2029,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2117,7 +2117,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2337,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,7 +2381,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,7 +2447,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,7 +2601,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2711,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,7 +2887,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,7 +3129,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,7 +3503,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3613,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3635,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3679,12 +3679,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3701,20 +3701,64 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3753,7 +3797,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
